--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA83"/>
+  <dimension ref="A1:AA85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -9545,6 +9545,168 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Mantra Free Shop</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Mantra Free Shop</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>86954</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Rivera</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>402 Avenida Sarandí</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://mantradutyfree.ecwid.com</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>mantradutyfree@gmail.com</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>+598 4623 8485</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mantra_free_shop/</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>Diego Sebastian</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diego-sebastian-gonzalez-b69bb1123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Los Molinos</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Los Molinos</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>122566</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, G</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>4523 Avenida Millán</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>11700</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>http://www.distribuidoralosmolinos.com.uy</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>losmolinos.mayorista@gmail.com</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/losmolinosdistribuidora/</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr"/>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Uruguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Uruguay.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA85"/>
+  <dimension ref="A1:AA87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -9707,6 +9707,168 @@
       <c r="Z85" s="2" t="inlineStr"/>
       <c r="AA85" s="2" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Mantra Free Shop</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Mantra Free Shop</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>86954</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Rivera</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Rivera</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>402 Avenida Sarandí</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://mantradutyfree.ecwid.com</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>mantradutyfree@gmail.com</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>+598 4623 8485</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mantra_free_shop/</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>Diego Sebastian</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diego-sebastian-gonzalez-b69bb1123/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Los Molinos</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Distribuidora Los Molinos</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>122566</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Montevideo</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Departamento de Montevideo, G</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>4523 Avenida Millán</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>11700</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>http://www.distribuidoralosmolinos.com.uy</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>losmolinos.mayorista@gmail.com</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/losmolinosdistribuidora/</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr"/>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
